--- a/Team-Data/2011-12/4-2-2011-12.xlsx
+++ b/Team-Data/2011-12/4-2-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -766,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="AM2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN2" t="n">
         <v>7</v>
@@ -793,13 +860,13 @@
         <v>10</v>
       </c>
       <c r="AV2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>13</v>
       </c>
       <c r="AX2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -811,7 +878,7 @@
         <v>20</v>
       </c>
       <c r="BB2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -984,7 +1051,7 @@
         <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-12.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1142,7 +1209,7 @@
         <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -1207,22 +1274,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>0.764</v>
+        <v>0.778</v>
       </c>
       <c r="H5" t="n">
         <v>48.1</v>
       </c>
       <c r="I5" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J5" t="n">
         <v>82.5</v>
@@ -1237,19 +1304,19 @@
         <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="P5" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.722</v>
+        <v>0.726</v>
       </c>
       <c r="R5" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="S5" t="n">
         <v>32.2</v>
@@ -1261,7 +1328,7 @@
         <v>23</v>
       </c>
       <c r="V5" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.1</v>
@@ -1279,10 +1346,10 @@
         <v>17.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD5" t="n">
         <v>1</v>
@@ -1297,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1309,7 +1376,7 @@
         <v>9</v>
       </c>
       <c r="AL5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
         <v>19</v>
@@ -1324,7 +1391,7 @@
         <v>21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>27</v>
@@ -1530,7 +1597,7 @@
         <v>27</v>
       </c>
       <c r="AY6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ6" t="n">
         <v>23</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" t="n">
         <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.556</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>35.8</v>
+        <v>35.9</v>
       </c>
       <c r="J7" t="n">
-        <v>81.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L7" t="n">
         <v>7.5</v>
@@ -1601,34 +1668,34 @@
         <v>22.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.331</v>
+        <v>0.334</v>
       </c>
       <c r="O7" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="P7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.758</v>
+        <v>0.761</v>
       </c>
       <c r="R7" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
         <v>32.4</v>
       </c>
       <c r="T7" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U7" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="V7" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X7" t="n">
         <v>5.1</v>
@@ -1637,40 +1704,40 @@
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
       </c>
       <c r="AF7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="n">
         <v>20</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
         <v>6</v>
@@ -1682,13 +1749,13 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
         <v>25</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>28</v>
@@ -1697,19 +1764,19 @@
         <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU7" t="n">
         <v>13</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>2</v>
@@ -1721,10 +1788,10 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -1831,13 +1898,13 @@
         <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
         <v>14</v>
@@ -1858,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN8" t="n">
         <v>23</v>
@@ -1888,7 +1955,7 @@
         <v>28</v>
       </c>
       <c r="AW8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2043,7 +2110,7 @@
         <v>27</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
         <v>15</v>
@@ -2052,7 +2119,7 @@
         <v>17</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>11</v>
@@ -2088,7 +2155,7 @@
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2299,61 +2366,61 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.537</v>
+        <v>0.528</v>
       </c>
       <c r="H11" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J11" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K11" t="n">
         <v>0.453</v>
       </c>
       <c r="L11" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M11" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O11" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="Q11" t="n">
         <v>0.785</v>
       </c>
       <c r="R11" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S11" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T11" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U11" t="n">
         <v>21</v>
       </c>
       <c r="V11" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2374,13 +2441,13 @@
         <v>98.09999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
         <v>15</v>
@@ -2389,7 +2456,7 @@
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
         <v>5</v>
@@ -2401,13 +2468,13 @@
         <v>11</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>15</v>
       </c>
       <c r="AN11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO11" t="n">
         <v>21</v>
@@ -2422,16 +2489,16 @@
         <v>15</v>
       </c>
       <c r="AS11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AT11" t="n">
         <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2559,16 +2626,16 @@
         <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2663,25 +2730,25 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J13" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.452</v>
@@ -2690,67 +2757,67 @@
         <v>7.6</v>
       </c>
       <c r="M13" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="N13" t="n">
         <v>0.351</v>
       </c>
       <c r="O13" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="R13" t="n">
         <v>12.1</v>
       </c>
       <c r="S13" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T13" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V13" t="n">
         <v>13.3</v>
       </c>
       <c r="W13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y13" t="n">
         <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>6</v>
       </c>
       <c r="AG13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
         <v>7</v>
@@ -2774,10 +2841,10 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2786,13 +2853,13 @@
         <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV13" t="n">
         <v>3</v>
@@ -2801,19 +2868,19 @@
         <v>10</v>
       </c>
       <c r="AX13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY13" t="n">
         <v>6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -3027,37 +3094,37 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F15" t="n">
         <v>22</v>
       </c>
       <c r="G15" t="n">
-        <v>0.569</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>82.8</v>
+        <v>82.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
         <v>3.8</v>
       </c>
       <c r="M15" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="N15" t="n">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="O15" t="n">
         <v>17.5</v>
@@ -3066,7 +3133,7 @@
         <v>23.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R15" t="n">
         <v>12.5</v>
@@ -3078,22 +3145,22 @@
         <v>42.3</v>
       </c>
       <c r="U15" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="V15" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W15" t="n">
         <v>9.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>19.9</v>
@@ -3102,22 +3169,22 @@
         <v>95.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
         <v>9</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
@@ -3126,7 +3193,7 @@
         <v>8</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3135,7 +3202,7 @@
         <v>29</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO15" t="n">
         <v>11</v>
@@ -3144,7 +3211,7 @@
         <v>13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>6</v>
@@ -3153,7 +3220,7 @@
         <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>24</v>
@@ -3171,7 +3238,7 @@
         <v>23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
         <v>15</v>
@@ -3180,7 +3247,7 @@
         <v>18</v>
       </c>
       <c r="BC15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3393,7 @@
         <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
         <v>25</v>
@@ -3335,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>16</v>
@@ -3356,7 +3423,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB16" t="n">
         <v>4</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -3391,112 +3458,112 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
         <v>28</v>
       </c>
       <c r="G17" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="H17" t="n">
         <v>48.1</v>
       </c>
       <c r="I17" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J17" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L17" t="n">
         <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="P17" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.786</v>
+        <v>0.787</v>
       </c>
       <c r="R17" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S17" t="n">
         <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U17" t="n">
         <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y17" t="n">
         <v>4.7</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
         <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="n">
         <v>19</v>
       </c>
       <c r="AG17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="n">
         <v>13</v>
       </c>
       <c r="AM17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN17" t="n">
         <v>14</v>
@@ -3532,7 +3599,7 @@
         <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
         <v>13</v>
@@ -3541,7 +3608,7 @@
         <v>18</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
         <v>25</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="n">
-        <v>0.455</v>
+        <v>0.463</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,19 +3658,19 @@
         <v>35.9</v>
       </c>
       <c r="J18" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M18" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O18" t="n">
         <v>19.8</v>
@@ -3612,22 +3679,22 @@
         <v>25.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R18" t="n">
         <v>12.5</v>
       </c>
       <c r="S18" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T18" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="U18" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W18" t="n">
         <v>7</v>
@@ -3639,16 +3706,16 @@
         <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA18" t="n">
         <v>21.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.6</v>
+        <v>-0.4</v>
       </c>
       <c r="AD18" t="n">
         <v>1</v>
@@ -3660,7 +3727,7 @@
         <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH18" t="n">
         <v>17</v>
@@ -3675,7 +3742,7 @@
         <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM18" t="n">
         <v>6</v>
@@ -3690,7 +3757,7 @@
         <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR18" t="n">
         <v>7</v>
@@ -3705,7 +3772,7 @@
         <v>25</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>25</v>
@@ -3723,10 +3790,10 @@
         <v>3</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>23</v>
@@ -3842,7 +3909,7 @@
         <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH19" t="n">
         <v>28</v>
@@ -3887,10 +3954,10 @@
         <v>22</v>
       </c>
       <c r="AV19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX19" t="n">
         <v>28</v>
@@ -3905,10 +3972,10 @@
         <v>16</v>
       </c>
       <c r="BB19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC19" t="n">
         <v>25</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>26</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>28</v>
@@ -4027,7 +4094,7 @@
         <v>28</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>28</v>
@@ -4075,13 +4142,13 @@
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>24</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF21" t="n">
         <v>16</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
         <v>21</v>
@@ -4221,13 +4288,13 @@
         <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
       </c>
       <c r="AN21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
         <v>6</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4301,37 +4368,37 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
         <v>40</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.755</v>
+        <v>0.769</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K22" t="n">
         <v>0.478</v>
       </c>
       <c r="L22" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M22" t="n">
         <v>19.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="O22" t="n">
         <v>20.9</v>
@@ -4340,7 +4407,7 @@
         <v>26.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R22" t="n">
         <v>10.7</v>
@@ -4352,34 +4419,34 @@
         <v>43.4</v>
       </c>
       <c r="U22" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="V22" t="n">
         <v>16.3</v>
       </c>
       <c r="W22" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X22" t="n">
         <v>7.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
         <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.2</v>
+        <v>103.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,10 +4458,10 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AI22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ22" t="n">
         <v>26</v>
@@ -4403,13 +4470,13 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM22" t="n">
         <v>12</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,7 +4494,7 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4436,7 +4503,7 @@
         <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>1.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>6</v>
@@ -4573,7 +4640,7 @@
         <v>6</v>
       </c>
       <c r="AH23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>27</v>
@@ -4597,7 +4664,7 @@
         <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>12</v>
@@ -4752,13 +4819,13 @@
         <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
         <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ24" t="n">
         <v>4</v>
@@ -4800,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
         <v>18</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE25" t="n">
         <v>18</v>
@@ -4943,7 +5010,7 @@
         <v>12</v>
       </c>
       <c r="AJ25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
@@ -5000,7 +5067,7 @@
         <v>15</v>
       </c>
       <c r="BC25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
       </c>
       <c r="F26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.463</v>
+        <v>0.472</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5053,22 +5120,22 @@
         <v>0.446</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="M26" t="n">
         <v>20.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.345</v>
+        <v>0.341</v>
       </c>
       <c r="O26" t="n">
         <v>17.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
         <v>11</v>
@@ -5080,7 +5147,7 @@
         <v>40.7</v>
       </c>
       <c r="U26" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
         <v>14.1</v>
@@ -5092,7 +5159,7 @@
         <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z26" t="n">
         <v>19.7</v>
@@ -5104,22 +5171,22 @@
         <v>97.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
       </c>
       <c r="AF26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5137,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO26" t="n">
         <v>12</v>
@@ -5152,7 +5219,7 @@
         <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
         <v>25</v>
@@ -5170,7 +5237,7 @@
         <v>15</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ26" t="n">
         <v>16</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC26" t="n">
         <v>16</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
         <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.358</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J27" t="n">
         <v>86.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.431</v>
+        <v>0.43</v>
       </c>
       <c r="L27" t="n">
         <v>6.3</v>
       </c>
       <c r="M27" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="N27" t="n">
         <v>0.313</v>
       </c>
       <c r="O27" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P27" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R27" t="n">
         <v>13.7</v>
       </c>
       <c r="S27" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T27" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U27" t="n">
         <v>18.8</v>
       </c>
       <c r="V27" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W27" t="n">
         <v>8.300000000000001</v>
@@ -5283,25 +5350,25 @@
         <v>20.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5.3</v>
+        <v>-5.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AF27" t="n">
         <v>25</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
         <v>11</v>
@@ -5313,10 +5380,10 @@
         <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AM27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN27" t="n">
         <v>28</v>
@@ -5328,13 +5395,13 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR27" t="n">
         <v>2</v>
       </c>
       <c r="AS27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -5343,7 +5410,7 @@
         <v>26</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
         <v>5</v>
@@ -5352,19 +5419,19 @@
         <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
         <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>-3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF29" t="n">
         <v>26</v>
@@ -5665,7 +5732,7 @@
         <v>27</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>25</v>
@@ -5692,7 +5759,7 @@
         <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>23</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5757,22 +5824,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F30" t="n">
         <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.519</v>
+        <v>0.509</v>
       </c>
       <c r="H30" t="n">
         <v>48.8</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
         <v>84.09999999999999</v>
@@ -5784,13 +5851,13 @@
         <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.306</v>
+        <v>0.307</v>
       </c>
       <c r="O30" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P30" t="n">
         <v>25</v>
@@ -5817,25 +5884,25 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y30" t="n">
         <v>5.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA30" t="n">
         <v>20.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
@@ -5874,13 +5941,13 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT30" t="n">
         <v>4</v>
@@ -5892,7 +5959,7 @@
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX30" t="n">
         <v>4</v>
@@ -5904,10 +5971,10 @@
         <v>29</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
-        <v>0.226</v>
+        <v>0.231</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,31 +6033,31 @@
         <v>5.2</v>
       </c>
       <c r="M31" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N31" t="n">
-        <v>0.321</v>
+        <v>0.319</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
         <v>21.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.726</v>
+        <v>0.722</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T31" t="n">
-        <v>41.5</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="V31" t="n">
         <v>15.3</v>
@@ -5999,31 +6066,31 @@
         <v>7.8</v>
       </c>
       <c r="X31" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
         <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.2</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.8</v>
+        <v>-6.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
@@ -6050,13 +6117,13 @@
         <v>24</v>
       </c>
       <c r="AO31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AP31" t="n">
         <v>19</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR31" t="n">
         <v>12</v>
@@ -6065,10 +6132,10 @@
         <v>21</v>
       </c>
       <c r="AT31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV31" t="n">
         <v>21</v>
@@ -6083,13 +6150,13 @@
         <v>7</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC31" t="n">
         <v>29</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-2-2011-12</t>
+          <t>2012-04-02</t>
         </is>
       </c>
     </row>
